--- a/Issues_No_Tests_v2.xlsx
+++ b/Issues_No_Tests_v2.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4149</v>
+        <v>4151</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>[BUG] run_style verlet/split fails for certain types of examples</t>
+          <t>[BUG] Inconsistent syntax for dump_modify triclinic/general</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/4149</t>
+          <t>https://github.com/lammps/lammps/issues/4151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/4291</t>
+          <t>https://github.com/lammps/lammps/pull/4152</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4291</v>
+        <v>4152</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Fixing the MPI memory violation and making run_style verlet/split work for systems lacking charge (e.g., dipole/spin KSpace) depends on correct scientific/algorithmic handling of electrostatics/KSpace data distribution and numerics rather than generic software behavior.</t>
+          <t>The bug concerns the parsing/semantic handling of the dump_modify triclinic/general option specifically affecting how triclinic/general simulation box geometry is interpreted in dump outputs, which is central scientific-software behavior.</t>
         </is>
       </c>
     </row>
@@ -1179,16 +1179,16 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4151</v>
+        <v>4106</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Inconsistent syntax for dump_modify triclinic/general</t>
+          <t>[BUG] Small error in in.ttm.mod example (Si.ttm_mod)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/4151</t>
+          <t>https://github.com/lammps/lammps/issues/4106</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1209,11 +1209,11 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/4152</t>
+          <t>https://github.com/lammps/lammps/pull/4134</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4152</v>
+        <v>4134</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>The bug concerns the parsing/semantic handling of the dump_modify triclinic/general option specifically affecting how triclinic/general simulation box geometry is interpreted in dump outputs, which is central scientific-software behavior.</t>
+          <t>The bug report claims that scientifically defined parameters (gamma_p and gamma_s) are swapped in the TTM-MD example, involving incorrect numerical/physical mapping of model coefficients and units.</t>
         </is>
       </c>
     </row>
@@ -1234,16 +1234,16 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4106</v>
+        <v>3936</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Small error in in.ttm.mod example (Si.ttm_mod)</t>
+          <t>[BUG] hybrid/overlay with KOKKOS overwrites atom forces, rather than sums them</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/4106</t>
+          <t>https://github.com/lammps/lammps/issues/3936</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1264,11 +1264,11 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/4134</t>
+          <t>https://github.com/lammps/lammps/pull/3930</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4134</v>
+        <v>3930</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>The bug report claims that scientifically defined parameters (gamma_p and gamma_s) are swapped in the TTM-MD example, involving incorrect numerical/physical mapping of model coefficients and units.</t>
+          <t>The bug causes incorrect force accumulation in LAMMPS hybrid/overlay when using KOKKOS (scientific simulation results become wrong due to improper force zeroing vs summation), which requires domain-specific understanding of the force computation/accumulation algorithm.</t>
         </is>
       </c>
     </row>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3936</v>
+        <v>3895</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>[BUG] hybrid/overlay with KOKKOS overwrites atom forces, rather than sums them</t>
+          <t>[BUG] Sporadic numeric breakdowns with ReaxFF+QEq using Kokkos on NVIDIA and AMD GPUs with tag stable_2Aug2023</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/3936</t>
+          <t>https://github.com/lammps/lammps/issues/3895</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1319,11 +1319,11 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/3930</t>
+          <t>https://github.com/lammps/lammps/pull/3898</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3930</v>
+        <v>3898</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1333,27 +1333,27 @@
       <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>The bug causes incorrect force accumulation in LAMMPS hybrid/overlay when using KOKKOS (scientific simulation results become wrong due to improper force zeroing vs summation), which requires domain-specific understanding of the force computation/accumulation algorithm.</t>
+          <t>The reported sporadic numeric breakdowns and QEq convergence failures in ReaxFF+QEq directly indicate domain-specific numerical/scientific behavior changes between builds/backends, requiring diagnosis of the underlying math/algorithmic numerics.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>lammps/lammps</t>
+          <t>biopython/biopython</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3895</v>
+        <v>3757</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Sporadic numeric breakdowns with ReaxFF+QEq using Kokkos on NVIDIA and AMD GPUs with tag stable_2Aug2023</t>
+          <t>Parsing Exonerate text output with SearchIO does not assign target strand correctly</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/3895</t>
+          <t>https://github.com/biopython/biopython/issues/3757</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1367,18 +1367,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
+      <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/3898</t>
+          <t>https://github.com/biopython/biopython/pull/3761</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3898</v>
+        <v>3761</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1388,27 +1384,27 @@
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>The reported sporadic numeric breakdowns and QEq convergence failures in ReaxFF+QEq directly indicate domain-specific numerical/scientific behavior changes between builds/backends, requiring diagnosis of the underlying math/algorithmic numerics.</t>
+          <t>Correctly parsing biological strand orientation from Exonerate text output into SearchIO hit_strand_all is a domain-specific scientific-data interpretation/algorithmic bug.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>biopython/biopython</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3757</v>
+        <v>16362</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Parsing Exonerate text output with SearchIO does not assign target strand correctly</t>
+          <t>Eliminate redundant transformations when drawing WCSAxes ticks/gridlines</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/biopython/biopython/issues/3757</t>
+          <t>https://github.com/astropy/astropy/issues/16362</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1422,354 +1418,354 @@
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/biopython/biopython/pull/3761</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>3761</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Correctly parsing biological strand orientation from Exonerate text output into SearchIO hit_strand_all is a domain-specific scientific-data interpretation/algorithmic bug.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>astropy/astropy</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>16362</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Eliminate redundant transformations when drawing WCSAxes ticks/gridlines</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/issues/16362</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Feature Request
 Performance
 visualization.wcsaxes</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>https://github.com/astropy/astropy/pull/16366</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>16366</v>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>The issue centers on optimizing expensive coordinate transforms and caching their numerical results correctly when WCS transforms may or may not change, which requires domain-specific understanding of WCSAxes transformation behavior.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>astropy/astropy</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>13986</v>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>LevMarLSQFitter crashes on perfectly benign input, claiming there are NaNs</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/issues/13986</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Bug
-modeling</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/pull/17850</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>17850</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>The crash is caused by numerical instability in the LevMarLSQFitter for large-valued PSF data, leading the objective function to produce non-finite values during optimization rather than due to truly non-finite inputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>qgis/QGIS</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>63868</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Concave Hull algorithm generates empty geometry</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>https://github.com/qgis/QGIS/issues/63868</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Processing
 Bug
 geos</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>https://github.com/qgis/QGIS/pull/64781</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>64781</v>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>The bug concerns a computational geometry algorithm (concave hull) interacting with GEOS triangulation producing an empty/failed hull from specific coordinate configurations, requiring numerical/scientific understanding of geometric algorithms and robustness.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>astropy/astropy</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>16372</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Faster checksum implementation</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>https://github.com/astropy/astropy/issues/16372</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Feature Request
 io.fits
 Performance</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>https://github.com/astropy/astropy/pull/17209</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>17209</v>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>This feature request is about optimizing the FITS checksum/datasum calculation algorithm for scientific file integrity, where correctness of the checksum implementation is mathematically/algorithmically central.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>qgis/QGIS</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>62157</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Error in counting tiles in each levels in Generate XYZ tiles (Directory)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>https://github.com/qgis/QGIS/issues/62157</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Processing
 Bug</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>https://github.com/qgis/QGIS/pull/66606</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>66606</v>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>The bug is about incorrect tile counting per zoom level in an XYZ tiles generation algorithm, which indicates a logic/numerical error in how zoom-level ranges are computed and aggregated.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>qiskit/qiskit</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>13355</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Faster hashing for Pauli operators.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>https://github.com/Qiskit/qiskit/issues/13355</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>type: feature request
 performance
 mod: quantum info</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/pull/13379</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>13379</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>This is about optimizing the hashing/labeling algorithm for Pauli operators in quantum information, which is domain-specific scientific software behavior affecting correctness-relevant internal computations (Pauli representation/evolution efficiency).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>qiskit/qiskit</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>12167</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Strange Behaviour of `sx` gate when defined inline in QASM</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/issues/12167</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>bug
+mod: qasm3</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/pull/12387</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>12387</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>The bug is caused by numerical expression evaluation in OpenQASM (`pow(1/2)` being treated as integer division), which directly affects gate semantics and therefore the computed quantum state probabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>qutip/qutip</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2575</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Segfaults in various functions when dimension is too large</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/qutip/qutip/issues/2575</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/pull/13379</t>
+          <t>https://github.com/qutip/qutip/pull/2582</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13379</v>
+        <v>2582</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1779,27 +1775,27 @@
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>This is about optimizing the hashing/labeling algorithm for Pauli operators in quantum information, which is domain-specific scientific software behavior affecting correctness-relevant internal computations (Pauli representation/evolution efficiency).</t>
+          <t>The bug is about numerical/data-dimension handling in QuTiP’s linear-algebra routines where large matrix dimensions lead to incorrect memory behavior (segfault vs MemoryError), which requires domain knowledge of scientific computing and numerical library interactions.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>qiskit/qiskit</t>
+          <t>qutip/qutip</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>12167</v>
+        <v>2530</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Strange Behaviour of `sx` gate when defined inline in QASM</t>
+          <t>Slow brmesolve() for certain problems &amp; bloch-redfield tensor always returned Dense</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/issues/12167</t>
+          <t>https://github.com/qutip/qutip/issues/2530</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1813,19 +1809,14 @@
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>bug
-mod: qasm3</t>
-        </is>
-      </c>
+      <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/pull/12387</t>
+          <t>https://github.com/qutip/qutip/pull/2541</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>12387</v>
+        <v>2541</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1835,27 +1826,27 @@
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>The bug is caused by numerical expression evaluation in OpenQASM (`pow(1/2)` being treated as integer division), which directly affects gate semantics and therefore the computed quantum state probabilities.</t>
+          <t>The bug concerns incorrect sparse/dense handling and a performance-impacting algorithmic path in Bloch-Redfield tensor construction/brmesolve that depends on scientific numerical linear-algebra choices.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>qutip/qutip</t>
+          <t>qutip/qutip-jax</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2575</v>
+        <v>47</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Segfaults in various functions when dimension is too large</t>
+          <t>Regarding Monte-Carlo quantum trajectories and measurements of observables on final states</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/2575</t>
+          <t>https://github.com/qutip/qutip-jax/issues/47</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1872,11 +1863,11 @@
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2582</t>
+          <t>https://github.com/qutip/qutip/pull/2493</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2582</v>
+        <v>2493</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1886,7 +1877,7 @@
       <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>The bug is about numerical/data-dimension handling in QuTiP’s linear-algebra routines where large matrix dimensions lead to incorrect memory behavior (segfault vs MemoryError), which requires domain knowledge of scientific computing and numerical library interactions.</t>
+          <t>The bug concerns domain-specific QuTiP JAX-based Monte-Carlo quantum trajectories/measurement pipelines and their numerical/solver integration, where incorrect integration or observable evaluation would affect scientific correctness.</t>
         </is>
       </c>
     </row>
@@ -1897,16 +1888,16 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2530</v>
+        <v>1919</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Slow brmesolve() for certain problems &amp; bloch-redfield tensor always returned Dense</t>
+          <t>Dicke Entropy returns -Inf</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/2530</t>
+          <t>https://github.com/qutip/qutip/issues/1919</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1920,14 +1911,18 @@
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>good first issue</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2541</t>
+          <t>https://github.com/qutip/qutip/pull/2466</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2541</v>
+        <v>2466</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1937,7 +1932,7 @@
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>The bug concerns incorrect sparse/dense handling and a performance-impacting algorithmic path in Bloch-Redfield tensor construction/brmesolve that depends on scientific numerical linear-algebra choices.</t>
+          <t>The bug is due to numerical issues in computing eigenvalues and entropy (negative values leading to -Inf), requiring scientific/numerical expertise to diagnose and fix correctly.</t>
         </is>
       </c>
     </row>
@@ -1948,16 +1943,16 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>47</v>
+        <v>2345</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Regarding Monte-Carlo quantum trajectories and measurements of observables on final states</t>
+          <t>Negativity function does not work</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip-jax/issues/47</t>
+          <t>https://github.com/qutip/qutip/issues/2345</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1967,18 +1962,27 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/qutip/qutip/assets/147247481/710869a8-79e6-4941-b6d6-2ad0cf9fd76d</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>BUG
+good first issue</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2493</t>
+          <t>https://github.com/qutip/qutip/pull/2371</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2493</v>
+        <v>2371</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -1988,7 +1992,7 @@
       <c r="L28" s="3" t="inlineStr"/>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>The bug concerns domain-specific QuTiP JAX-based Monte-Carlo quantum trajectories/measurement pipelines and their numerical/solver integration, where incorrect integration or observable evaluation would affect scientific correctness.</t>
+          <t>Fixing the broken negativity calculation due to an incorrect `partial_transpose()` import/type error requires domain-relevant scientific-software knowledge about the algorithm and its implementation.</t>
         </is>
       </c>
     </row>
@@ -1999,16 +2003,16 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1919</v>
+        <v>2299</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Dicke Entropy returns -Inf</t>
+          <t>MemoryError when updating to latest qutip</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/1919</t>
+          <t>https://github.com/qutip/qutip/issues/2299</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2022,18 +2026,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>good first issue</t>
-        </is>
-      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2466</t>
+          <t>https://github.com/qutip/qutip/pull/2303</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2466</v>
+        <v>2303</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>The bug is due to numerical issues in computing eigenvalues and entropy (negative values leading to -Inf), requiring scientific/numerical expertise to diagnose and fix correctly.</t>
+          <t>The bug involves QuTiP’s stochastic Schrödinger solver and how trajectory states are averaged/converted to density matrices, leading to a numerical performance/memory failure that requires domain-specific understanding to fix correctly.</t>
         </is>
       </c>
     </row>
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2345</v>
+        <v>2009</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Negativity function does not work</t>
+          <t>`visualization.hinton` plots matrix transpose instead of matrix</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/2345</t>
+          <t>https://github.com/qutip/qutip/issues/2009</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2078,22 +2078,18 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/assets/147247481/710869a8-79e6-4941-b6d6-2ad0cf9fd76d</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>BUG
-good first issue</t>
-        </is>
-      </c>
+          <t>https://user-images.githubusercontent.com/38159029/197494500-d3b3ab8a-59a7-4bee-b55e-94a5e44f02ba.png
+https://user-images.githubusercontent.com/38159029/197494815-885be8c9-dc3f-4b4c-a594-234220c06b41.png</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2371</t>
+          <t>https://github.com/qutip/qutip/pull/2011</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2371</v>
+        <v>2011</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -2103,7 +2099,7 @@
       <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Fixing the broken negativity calculation due to an incorrect `partial_transpose()` import/type error requires domain-relevant scientific-software knowledge about the algorithm and its implementation.</t>
+          <t>The bug is that the `hinton` visualization is plotting the matrix transpose instead of the matrix itself, which is a scientific/data-mapping error requiring mathematical/numerical understanding of the intended array orientation.</t>
         </is>
       </c>
     </row>
@@ -2114,21 +2110,21 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2299</v>
+        <v>1128</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>MemoryError when updating to latest qutip</t>
+          <t>Husimi Q and Wigner spin functions don't give correct results</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/2299</t>
+          <t>https://github.com/qutip/qutip/issues/1128</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2137,14 +2133,18 @@
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2303</t>
+          <t>https://github.com/qutip/qutip/pull/1195</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2303</v>
+        <v>1195</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>The bug involves QuTiP’s stochastic Schrödinger solver and how trajectory states are averaged/converted to density matrices, leading to a numerical performance/memory failure that requires domain-specific understanding to fix correctly.</t>
+          <t>The bug reports incorrect scientific results for Husimi Q and Wigner spin functions and traces the error to a mathematical factor/order and spin-coherent state implementation, requiring domain-specific physics/numerical knowledge to diagnose and fix.</t>
         </is>
       </c>
     </row>
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2009</v>
+        <v>1204</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>`visualization.hinton` plots matrix transpose instead of matrix</t>
+          <t>vector_to_operator throws Exception with qutip 4.5</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/2009</t>
+          <t>https://github.com/qutip/qutip/issues/1204</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2184,23 +2184,18 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/38159029/197494500-d3b3ab8a-59a7-4bee-b55e-94a5e44f02ba.png
-https://user-images.githubusercontent.com/38159029/197494815-885be8c9-dc3f-4b4c-a594-234220c06b41.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2011</t>
+          <t>https://github.com/qutip/qutip/pull/1475</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2011</v>
+        <v>1475</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2210,7 +2205,7 @@
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>The bug is that the `hinton` visualization is plotting the matrix transpose instead of the matrix itself, which is a scientific/data-mapping error requiring mathematical/numerical understanding of the intended array orientation.</t>
+          <t>Diagnosing and fixing the failure in qutip.vector_to_operator requires understanding the underlying linear-algebra/numerical representation of operator-kets, tensor-product dimensions, and matrix reshaping behavior.</t>
         </is>
       </c>
     </row>
@@ -2221,21 +2216,21 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1128</v>
+        <v>1451</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Husimi Q and Wigner spin functions don't give correct results</t>
+          <t>TestDicke fails with scipy 1.6.1: TypeError: can't convert complex to float</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/1128</t>
+          <t>https://github.com/qutip/qutip/issues/1451</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2246,16 +2241,16 @@
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>BUG</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/1195</t>
+          <t>https://github.com/qutip/qutip/pull/1452</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1195</v>
+        <v>1452</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -2265,7 +2260,7 @@
       <c r="L33" s="3" t="inlineStr"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>The bug reports incorrect scientific results for Husimi Q and Wigner spin functions and traces the error to a mathematical factor/order and spin-coherent state implementation, requiring domain-specific physics/numerical knowledge to diagnose and fix.</t>
+          <t>The bug is triggered by sparse matrix construction with complex data after a specific SciPy version change, requiring numerical/scientific-software knowledge about dtype handling for correct matrix generation.</t>
         </is>
       </c>
     </row>
@@ -2276,16 +2271,16 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1204</v>
+        <v>1406</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>vector_to_operator throws Exception with qutip 4.5</t>
+          <t>Segmentation fault while trying to make large tensor product</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/1204</t>
+          <t>https://github.com/qutip/qutip/issues/1406</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2299,14 +2294,18 @@
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/1475</t>
+          <t>https://github.com/qutip/qutip/pull/1436</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1475</v>
+        <v>1436</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -2316,7 +2315,7 @@
       <c r="L34" s="3" t="inlineStr"/>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Diagnosing and fixing the failure in qutip.vector_to_operator requires understanding the underlying linear-algebra/numerical representation of operator-kets, tensor-product dimensions, and matrix reshaping behavior.</t>
+          <t>The bug is a low-level crash triggered by a scientific computation (large tensor product/qubit state construction) where correct handling should occur, so diagnosing/fixing it involves domain-specific numerical/software behavior.</t>
         </is>
       </c>
     </row>
@@ -2327,16 +2326,16 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1451</v>
+        <v>425</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>TestDicke fails with scipy 1.6.1: TypeError: can't convert complex to float</t>
+          <t>Qobj trunc_neg causing Travis errors</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/1451</t>
+          <t>https://github.com/qutip/qutip/issues/425</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2350,18 +2349,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>BUG</t>
-        </is>
-      </c>
+      <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/1452</t>
+          <t>https://github.com/qutip/qutip/pull/428</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1452</v>
+        <v>428</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -2371,7 +2366,7 @@
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>The bug is triggered by sparse matrix construction with complex data after a specific SciPy version change, requiring numerical/scientific-software knowledge about dtype handling for correct matrix generation.</t>
+          <t>The issue is about a numerical truncation method (Qobj.trunc_neg) producing an IndexError during tests, which requires understanding the scientific/numerical behavior of operator truncation.</t>
         </is>
       </c>
     </row>
@@ -2382,16 +2377,16 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1406</v>
+        <v>257</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Segmentation fault while trying to make large tensor product</t>
+          <t>Hadamard transform normalisation factor incorrect</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/1406</t>
+          <t>https://github.com/qutip/qutip/issues/257</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2405,18 +2400,14 @@
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>BUG</t>
-        </is>
-      </c>
+      <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/1436</t>
+          <t>https://github.com/qutip/qutip/pull/259</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1436</v>
+        <v>259</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -2426,27 +2417,27 @@
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>The bug is a low-level crash triggered by a scientific computation (large tensor product/qubit state construction) where correct handling should occur, so diagnosing/fixing it involves domain-specific numerical/software behavior.</t>
+          <t>The bug reports an incorrect Hadamard transform normalisation constant (0.5 vs 1/sqrt(2)) due to a mathematical/numerical division issue, requiring domain knowledge to diagnose and fix.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>qutip/qutip</t>
+          <t>deepchem/deepchem</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>425</v>
+        <v>2615</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Qobj trunc_neg causing Travis errors</t>
+          <t>GaussianHyperParameter failing test</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/425</t>
+          <t>https://github.com/deepchem/deepchem/issues/2615</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2456,18 +2447,22 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/32259379/126771448-eaebfbea-98ea-4dec-87d8-4ba6ce3d3938.png</t>
+        </is>
+      </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/428</t>
+          <t>https://github.com/deepchem/deepchem/pull/2620</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>428</v>
+        <v>2620</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -2477,27 +2472,27 @@
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>The issue is about a numerical truncation method (Qobj.trunc_neg) producing an IndexError during tests, which requires understanding the scientific/numerical behavior of operator truncation.</t>
+          <t>The failure is due to numerical optimization behavior (random initialization and handling of duplicate proposed points) affecting the recorded minimum value, requiring domain-specific understanding to diagnose and fix.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>qutip/qutip</t>
+          <t>deepchem/deepchem</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>257</v>
+        <v>2126</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hadamard transform normalisation factor incorrect</t>
+          <t>Errors while calculating `vina_energy_term`</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/257</t>
+          <t>https://github.com/deepchem/deepchem/issues/2126</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2514,11 +2509,11 @@
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/259</t>
+          <t>https://github.com/deepchem/deepchem/pull/2132</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>259</v>
+        <v>2132</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -2528,7 +2523,7 @@
       <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>The bug reports an incorrect Hadamard transform normalisation constant (0.5 vs 1/sqrt(2)) due to a mathematical/numerical division issue, requiring domain knowledge to diagnose and fix.</t>
+          <t>The bug concerns numerical tensor shape handling in the `vina_energy_term`/`weighted_linear_sum` calculation and incorrect math implementation for general `M` values, which is central scientific computation logic.</t>
         </is>
       </c>
     </row>
@@ -2539,16 +2534,16 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2615</v>
+        <v>1891</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GaussianHyperParameter failing test</t>
+          <t>dc.metrics.balanced_accuracy_score is broken</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepchem/deepchem/issues/2615</t>
+          <t>https://github.com/deepchem/deepchem/issues/1891</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2558,22 +2553,22 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/32259379/126771448-eaebfbea-98ea-4dec-87d8-4ba6ce3d3938.png</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepchem/deepchem/pull/2620</t>
+          <t>https://github.com/deepchem/deepchem/pull/1896</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2620</v>
+        <v>1896</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -2583,7 +2578,7 @@
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>The failure is due to numerical optimization behavior (random initialization and handling of duplicate proposed points) affecting the recorded minimum value, requiring domain-specific understanding to diagnose and fix.</t>
+          <t>The bug concerns a broken call to a metric function and requires correct scientific/ML evaluation logic by using the proper sklearn balanced_accuracy_score signature with sample_weight.</t>
         </is>
       </c>
     </row>
@@ -2594,16 +2589,16 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2126</v>
+        <v>1716</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Errors while calculating `vina_energy_term`</t>
+          <t>use_chirality in WeaveFeaturizer</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepchem/deepchem/issues/2126</t>
+          <t>https://github.com/deepchem/deepchem/issues/1716</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2617,14 +2612,19 @@
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>bug
+Contribution Welcome</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepchem/deepchem/pull/2132</t>
+          <t>https://github.com/deepchem/deepchem/pull/1769</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2132</v>
+        <v>1769</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -2633,117 +2633,6 @@
       </c>
       <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>The bug concerns numerical tensor shape handling in the `vina_energy_term`/`weighted_linear_sum` calculation and incorrect math implementation for general `M` values, which is central scientific computation logic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>deepchem/deepchem</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1891</v>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>dc.metrics.balanced_accuracy_score is broken</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/issues/1891</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/pull/1896</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>1896</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>The bug concerns a broken call to a metric function and requires correct scientific/ML evaluation logic by using the proper sklearn balanced_accuracy_score signature with sample_weight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>deepchem/deepchem</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>1716</v>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>use_chirality in WeaveFeaturizer</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/issues/1716</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>bug
-Contribution Welcome</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/pull/1769</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1769</v>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>The bug involves a domain-specific graph-featurization parameter (bond/traversal length) whose correct behavior depends on how chirality features change feature dimensionality.</t>
         </is>
@@ -2792,11 +2681,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2700,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2715,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2726,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
